--- a/src/actualizar_precios/actualizar_precios.xlsx
+++ b/src/actualizar_precios/actualizar_precios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:D422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>codigo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado Ejecucion</t>
         </is>
       </c>
     </row>
@@ -452,11 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1606625</v>
+        <v>450100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0201</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -467,11 +477,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1107100</v>
+        <v>820100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0154</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -482,11 +497,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>487100</v>
+        <v>400100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0194</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -497,11 +517,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>312100</v>
+        <v>235100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0103</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -512,11 +537,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>666100</v>
+        <v>450100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>666100 no esta dentro del rango 720000 a 990000</t>
+          <t>T0195</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -527,11 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>552100</v>
+        <v>420100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -542,11 +577,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>597100</v>
+        <v>510100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0123</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>510100.0 no está dentro del rango 581000.0 a 913000.0</t>
         </is>
       </c>
     </row>
@@ -557,11 +597,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1039100</v>
+        <v>423100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0196</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>423100.0 no está dentro del rango 770000.0 a 1210000.0</t>
         </is>
       </c>
     </row>
@@ -572,11 +617,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>685100</v>
+        <v>330100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0144</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -587,11 +637,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>806100</v>
+        <v>360100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0149</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -602,11 +657,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>417100</v>
+        <v>340100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0088</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -617,11 +677,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>450100</v>
+        <v>290100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0102</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -632,11 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1428925</v>
+        <v>720100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0193</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -647,11 +717,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>526100</v>
+        <v>320100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0197</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>320100.0 no está dentro del rango 442670.0 a 695624.0</t>
         </is>
       </c>
     </row>
@@ -662,11 +737,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>607100</v>
+        <v>345100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0011</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -677,11 +757,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>695100</v>
+        <v>660100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0097</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -692,11 +777,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>707100</v>
+        <v>290100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0130</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>290100.0 no está dentro del rango 560000.0 a 880000.0</t>
         </is>
       </c>
     </row>
@@ -707,11 +797,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>572100</v>
+        <v>330100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0168</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -722,11 +817,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>997100</v>
+        <v>800100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0148</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -737,11 +837,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>415100</v>
+        <v>360100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0051</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -752,11 +857,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>562100</v>
+        <v>420100</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0076</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -767,9 +877,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>717100</v>
+        <v>647100</v>
       </c>
       <c r="C23" t="inlineStr">
+        <is>
+          <t>T0146</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>exitosa</t>
         </is>
@@ -782,11 +897,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>772100</v>
+        <v>470100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0077</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -797,11 +917,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>806100</v>
+        <v>420100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0150</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>420100.0 no está dentro del rango 658000.0 a 1034000.0</t>
         </is>
       </c>
     </row>
@@ -812,11 +937,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>907100</v>
+        <v>460100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>907100 no esta dentro del rango 997810 a 725680</t>
+          <t>T0189</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>460100.0 no está dentro del rango 700000.0 a 1100000.0</t>
         </is>
       </c>
     </row>
@@ -827,11 +957,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>882100</v>
+        <v>670100</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0122</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -842,11 +977,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1005100</v>
+        <v>770100</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0121</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -857,116 +997,156 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1107100</v>
+        <v>570100</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0202</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>570100.0 no está dentro del rango 840000.0 a 1320000.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Oppo Reno7 256Gb 4G Dorado</t>
+          <t>Samsung Galaxy A04 64Gb Negro</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1140100</v>
+        <v>220100</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0072</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A04 64Gb Negro</t>
+          <t>Samsung Galaxy A04E 32Gb Azul</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>295100</v>
+        <v>220100</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>295100 no esta dentro del rango 448000 a 800000</t>
+          <t>T0074</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A04E 32Gb Azul</t>
+          <t>Samsung Galaxy A04S 128Gb Negro</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>307100</v>
+        <v>270100</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>307100 no esta dentro del rango 400000 a 640000</t>
+          <t>T0071</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A04S 128Gb Negro</t>
+          <t>Samsung Galaxy A05 128Gb Negro</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>457100</v>
+        <v>390100</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>457100 no esta dentro del rango 492800 a 880000</t>
+          <t>T0157</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>390100.0 no está dentro del rango 490000.0 a 770000.0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A05 128Gb Negro</t>
+          <t>Samsung Galaxy A05 64Gb Negro</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>517100</v>
+        <v>430100</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0158</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>430100.0 no está dentro del rango 441000.0 a 693000.0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A05 64Gb Negro</t>
+          <t>Samsung Galaxy A05S 128Gb Negro</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>477100</v>
+        <v>522100</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0170</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>522100.0 no está dentro del rango 560000.0 a 880000.0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A05S 128Gb Negro</t>
+          <t>Samsung Galaxy A14 128 Negro</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>606100</v>
+        <v>210100</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0089</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
@@ -977,249 +1157,334 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>587100</v>
+        <v>210100</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0095</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A14 128</t>
+          <t>Samsung Galaxy A15 128Gb Azul</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>587100</v>
+        <v>572100</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0159</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>572100.0 no está dentro del rango 607000.0 a 968000.0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A15 128Gb Azul</t>
+          <t>Samsung Galaxy A24 128 Negro</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>747100</v>
+        <v>317100</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0096</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>317100.0 no está dentro del rango 700000.0 a 1100000.0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A24 128 Negro</t>
+          <t>Samsung Galaxy A34 256Gb Negro</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>607100</v>
+        <v>520150</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0126</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A34 256Gb Negro</t>
+          <t>Samsung Galaxy A54 128Gb Negro</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1407150</v>
+        <v>520100</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0171</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A54 128Gb Negro</t>
+          <t>Samsung Galaxy A34 128GB Negro</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>695100</v>
+        <v>420150</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>695100 no esta dentro del rango 758480 a 1300000</t>
+          <t>T0098</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A34 128GB Negro</t>
+          <t>Tcl 408 64Gb T507J Azul</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1057150</v>
+        <v>250100</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0180</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tcl 408 64Gb T507J Azul</t>
+          <t>Tcl 40Se 128Gb Gris</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>457100</v>
+        <v>300100</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0181</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tcl 40Se 128Gb Gris</t>
+          <t>Tcl 40Se 256Gb Gris</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>487100</v>
+        <v>440100</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0182</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tcl 40Se 256Gb Gris</t>
+          <t>Tecno Camon 19 Neo 128Gb Blanco</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>666100</v>
+        <v>370100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0136</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tecno Camon 19 Neo 128Gb Blanco</t>
+          <t>Tecno Mobile Camon 20 256Gb Negro</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>495100</v>
+        <v>320100</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0140</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tecno Mobile Camon 20 256Gb Negro</t>
+          <t>Tecno Mobile Spark 10 Pro 256Gb Azul</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>907100</v>
+        <v>470100</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0139</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tecno Mobile Spark 10 Pro 256Gb Azul</t>
+          <t>Tecno Mobile Spark 20 256Gb Blanco</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>687100</v>
+        <v>410100</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0174</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>410100.0 no está dentro del rango 490000.0 a 850000.0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tecno Mobile Spark 20 256Gb Blanco</t>
+          <t>Tecno Spark 20 Pro Plus 256Gb Negro</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>705100</v>
+        <v>570100</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0188</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>570100.0 no está dentro del rango 651000.0 a 1023000.0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tecno Spark 20 Pro Plus 256Gb Negro</t>
+          <t>Tecno Spark 8C 128Gb Gris</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1107100</v>
+        <v>250100</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1107100 no esta dentro del rango 792000 a 1089000</t>
+          <t>T0108</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tecno Spark 8C 128Gb Gris</t>
+          <t>Tecno Spark 9Pro 128Gb Azul</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>396100</v>
+        <v>230100</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0177</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tecno Spark 9Pro 128Gb Azul</t>
+          <t>Tecno  Spark Go 2024 128Gb Blanco</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>507100</v>
+        <v>465100</v>
       </c>
       <c r="C53" t="inlineStr">
+        <is>
+          <t>T0187</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>exitosa</t>
         </is>
@@ -1228,1975 +1493,6848 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Tecno  Spark Go 2024 128Gb Blanco</t>
+          <t>Tecno Spark Go 2024 64Gb Blanco</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>506100</v>
+        <v>230100</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0172</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tecno Spark Go 2024 64Gb Blanco</t>
+          <t>Vivo Y16 128Gb Dorado</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>437100</v>
+        <v>310100</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0084</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Vivo Y16 128Gb Dorado</t>
+          <t>VIVO Y17s 128GB Verde</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>687100</v>
+        <v>420100</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0138</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VIVO Y17s 128GB Verde</t>
+          <t>Vivo Y22S 128Gb Azul Claro</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>737100</v>
+        <v>640100</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0085</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Vivo Y22S 128Gb Azul Claro</t>
+          <t>VIVO Y27 128GB Azul</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>775100</v>
+        <v>305100</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0147</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VIVO Y27 128GB Azul</t>
+          <t>Xiaomi Redmi 12 128Gb Azul</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>757100</v>
+        <v>320100</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0110</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>320100.0 no está dentro del rango 525000.0 a 825000.0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Vivo Y35 128Gb Dorado</t>
+          <t>Xiaomi Redmi 12C 128Gb Azul</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1005100</v>
+        <v>318100</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0078</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 12 128Gb Azul</t>
+          <t>Xiaomi Redmi 12C 64Gb Gris</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>707100</v>
+        <v>260100</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0113</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 12C 128Gb Azul</t>
+          <t>Xiaomi Redmi 13C 128Gb Azul</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>592100</v>
+        <v>265100</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0127</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>265100.0 no está dentro del rango 504000.0 a 792000.0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 12C 64Gb Gris</t>
+          <t>Xiaomi Redmi 13C 128Gb Azul</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>305100</v>
+        <v>265100</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0156</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 13C 128Gb Azul</t>
+          <t>Xiaomi Redmi 13C 256Gb Azul</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>587100</v>
+        <v>420100</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0131</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>420100.0 no está dentro del rango 817530.0 a 1359900.0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 13C 128Gb</t>
+          <t>Xiaomi Redmi Note 11 128gb Gris</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>587100</v>
+        <v>610100</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0024</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 13C 256Gb Azul</t>
+          <t>Xiaomi Redmi Note 12 128Gb Negro</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>727100</v>
+        <v>390100</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0120</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi Note 11 128gb Gris</t>
+          <t>Xiaomi Redmi Note 12 128Gb Negro</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>595100</v>
+        <v>390100</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>595100 no esta dentro del rango 604080 a 875000</t>
+          <t>T0093</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>390100.0 no está dentro del rango 612500.0 a 962500.0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi Note 12 128Gb Negro</t>
+          <t>Xiaomi Redmi Note 13 256Gb Azul</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>971100</v>
+        <v>521100</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>971100 no esta dentro del rango 621680 a 880000</t>
+          <t>T0169</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>521100.0 no está dentro del rango 735000.0 a 1155000.0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi Note 12 128Gb</t>
+          <t>Xiaomi Redmi Note 13 Pro 256Gb Negro</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>971100</v>
+        <v>872100</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>971100 no esta dentro del rango 621680 a 962500</t>
+          <t>T0161</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi Note 13 256Gb Azul</t>
+          <t>Xiaomi Redmi 12 256Gb Azul</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>907100</v>
+        <v>420100</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0114</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>420100.0 no está dentro del rango 616000.0 a 968000.0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi Note 13 Pro 256Gb Negro</t>
+          <t>Samsung Galaxy A15 5G 256Gb Azul</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1107100</v>
+        <v>620100</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>exitosa</t>
+          <t>T0210</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>620100.0 no está dentro del rango 693000.0 a 1089000.0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 12 256Gb Azul</t>
+          <t>Xiaomi Redmi 13C 256Gb Azul</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1007100</v>
+        <v>420100</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1007100 no esta dentro del rango 589680 a 968000</t>
+          <t>T0209</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>420100.0 no está dentro del rango 434630.0 a 682990.0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EXSA0364GPROM</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>Xiaomi A3 64Gb Negro</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>352100</v>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0190</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HONOR MAGIC 5 LITE 128GB 6RAM</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>Vivo Y03 128Gb Negro</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>488100</v>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0212</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>INFINIX HELIO G88 8RAM 8GB</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>Vivo Y27S 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>440100</v>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0213</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INFINIX HOT 30 PLAY 128GB 8 RAM</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>Samsung Galaxy A15 5G 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>620100</v>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0186</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>620100.0 no está dentro del rango 665000.0 a 1045000.0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INFINIX HOT 30i 128GB 4 RAM</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>Vivo Y18 128Gb Azul</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>510100</v>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0234</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>INFINIX HOT 40 PRO 8RAM 256GM</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>Vivo Y38 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>810100</v>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0235</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>INFINIX HOT 40I 128GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>Samsung Galaxy A25 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>820100</v>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0229</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>INFINIX HOT 40I 256 GB 8RAM</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>Tcl 50 Se 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>450100</v>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0238</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>INFINIX NOTE 30 256 GB 8 RAM</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>Honor X6A 128Gb Azul Claro</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>440100</v>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0216</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>440100.0 no está dentro del rango 476000.0 a 748000.0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>INFINIX NOTE 30 PRO 256GB 8RAM</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>Motorola Moto G04S 128Gb Azul</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>502100</v>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0230</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>INFINIX NOTE 40 256GB 8RAM</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>Xiaomi Redmi 14C 128Gb Azul</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>532100</v>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0249</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>INFINIX SMART 8 128GBGB 4RAM</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>Xiaomi Redmi 14C 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>622100</v>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0615</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>INFINIX SMART 8 128GM 4RAM</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>Xiaomi Redmi 14C 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>622100</v>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0616</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>INFINIX SMART 8 64GB 3RAM</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>Motorola Moto G34 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>875100</v>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0233</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>INFINIX ZERO 30 256GB 8RAM</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>Honor Magic 6 Lite 256Gb Plata</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1194100</v>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0246</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>INIFINIX SMARTH 7 HD 64GB 2 RAM</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>Honor X8B 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>820100</v>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0599</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MOTO E22I 64GB 2GB RAM</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>Motorola Moto G24 Power 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>752100</v>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0231</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MOTO G13 128GB 4 RAM</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>Oppo A40 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>680100</v>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0620</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MOTO G24 256GB 8RAM</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>Oppo A80 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1022100</v>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0609</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MOTO G52 128GB 6 RAM</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>Samsung Galaxy A06 128GB Negro</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>522100</v>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0600</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MOTO G52 256GB 6RAM</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>Vivo Y18 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>640100</v>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0236</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>640100.0 no está dentro del rango 651000.0 a 1023000.0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MOTO G60S 128GB 6 RAM</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>Samsung Galaxy A35 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>920150</v>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0217</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MOTOROLA DEFY 64 GB + 4 GB RAM</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>Honor X6B 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>722100</v>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0633</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MOTOROLA E20 32GB 2RAM</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>Xiaomi Redmi Note 13 256Gb 5G Negro</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>884100</v>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0608</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MOTOROLA E40 64GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>Tecno Mobile Camon 30 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>715100</v>
+      </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0226</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MOTOROLA E40 64GB 4RAM + POSTPAGO 60 GB +ACCESORIO</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>Tecno Mobile Spark 30 256Gb Blanco</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>922100</v>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0631</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MOTOROLA E6I 32GB 4 RAM</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>Samsung Galaxy A55 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>945150</v>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0243</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MOTOROLA G14 128GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>Honor 200 Lite 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>906100</v>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0630</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MOTOROLA G20 128GB 4GB RAM</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>Honor 200 Smart 256Gb Verde</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1122100</v>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0666</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MOTOROLA G20 32GB 3RAM</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>Zte V50 Design 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>430100</v>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0597</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MOTOROLA G20 64GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>Oppo A60 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>799100</v>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0667</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>799100.0 no está dentro del rango 805000.0 a 1265000.0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MOTOROLA G31 128GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>Xiaomi Re Note 13 Pro 5G 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1020100</v>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0665</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MOTOROLA G32 128GB + 4GB RAM</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>Honor X5B 128Gb Azul</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>622100</v>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0662</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MOTOROLA G41 64GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>Samsung Galaxy A16 256Gb Gris</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>922100</v>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0685</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MOTOROLA G50 5G 128gb 4RAM</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>Tecno Mobile Spark Go 1 128Gb Negro</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>542100</v>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0613</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MOTOROLA G51 128GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>Honor X7C 256Gb Blanco</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>922100</v>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0692</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MOTOROLA G51 5G 128GB 4 RAM</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>Tecno Mobile Spark 30C 256Gb Blanco</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>852100</v>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0612</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>852100.0 no está dentro del rango 490000.0 a 770000.0</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MOTOROLA G60 128GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>Tecno Mobile Spark 30C 256Gb Blanco</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>852100</v>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0604</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>852100.0 no está dentro del rango 525000.0 a 825000.0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MOTOROLA MOTO E30 32GB 2RAM</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>Motorola Moto G85 5G 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1042100</v>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0712</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MOTOROLA MOTO G41 128GB 4GB RAM</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>Samsung Galaxy A16 256Gb Gris</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>922100</v>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0710</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NOKIA C21 32GB</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>Xiaomi Redmi Note 14 Pro 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1215100</v>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0707</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NOKIA C21 PLUS 64GB</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>Xiaomi Redmi Note 14 256Gb 5G Negro</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1122100</v>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0751</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NOKIA G11 PLUS 64GB</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>Vivo Y19S 256GB Negro</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>822100</v>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0695</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NOKIA G21 128GB</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>Motorola Edge 50 Fusi 5G 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>920100</v>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0663</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OPPO RENO 6 LITE 128GB 6 RAM</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>Zte Blade A75 128Gb 5G Negro</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>482100</v>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0802</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OPPO RENO 7 128GB 6 RAM</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>Zte Nubia Neo 2 256Gb Gris</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>922100</v>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0721</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PRODUCTO PRUEBA</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>Xiaomi Redmi Not 14Pro256Gb 5G Negro</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1822101</v>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0732</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REALME C11 32GB 2RAM</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+          <t>Xiaomi Redmi Note 14 Pro 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1215100</v>
+      </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0739</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REALME C30S 64GB 3RAM</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>Motorola Moto G04S 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>554100</v>
+      </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0808</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>554100.0 no está dentro del rango 563420.0 a 885374.0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>REALME C51 128GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>Vivo V30 Se 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1020100</v>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0677</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REALME C53 128GB 6RAM</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>Vivo Y39 256Gb 5G Morado</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1215100</v>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0821</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>REALME C53 256GB 8RAM</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>Samsung Galaxy A26 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1122100</v>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0733</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>REALME C55 256GB 8 RAM</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>Samsung Galaxy A26 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1122100</v>
+      </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0822</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>REALME C67 256GB 8RAM</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>Samsung Galaxy A36 256Gb 5G Negro</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1722150</v>
+      </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0827</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>REDMI 10 5G 128GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>Vivo V30 Se 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1020100</v>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0741</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>REDMI 10A 64GB 4GB RAM</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>Xiaomi Redmi A5 128Gb Azul</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>522100</v>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0835</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>REDMI 10C 64GB 4GB RAM</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>Honor X8C 512Gb Verde</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1072100</v>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0842</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>REDMI 12C 64GB 3 RAM</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>Samsung Galaxy A56 256Gb 5G Negro</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2022149</v>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0105</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>REDMI A1 32GB 2GB RAM</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>Vivo Y04 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>762100</v>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0866</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>REDMI A3 64GB 3RAM</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>Xiaomi Redmi Note 14 256Gb 4G Negro</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>922100</v>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0708</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>REDMI NOTE 10 5G 128GB 4GB RAM</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>Oppo A5 Pro 256Gb Cafe</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1634060</v>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0834</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>REDMI NOTE 10S 128GB 6GB RAM</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>Oppo A5 256Gb Blanco</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1122100</v>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0892</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>REDMI NOTE 11S 128GB 6RAM</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>Honor X6C 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>822100</v>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0873</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>REDMI NOTE 13 128GB 6RAM</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>Motorola Moto G15 512Gb Azul</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>722100</v>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0897</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>REDMI NOTE 13 PRO 128GB 8RAM</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>Tecno Mobile Spark 30C 256Gb Blanco</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>852100</v>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0815</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Samsung A03 32gb</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+          <t>Motorola Edge 60 Fusion 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1215100</v>
+      </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0136</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>codigo no encontrado en la pagina</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SAMSUNG A03 64GB</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>Motorola Edge 60 Fusion 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1215100</v>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0863</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SAMSUNG A03 64GB + POSTPAGO 60 GB +ACCESORIO</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>Mot Moto G05 256Gbcon Motog05  Rojo</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1122100</v>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TC0003</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>1122100.0 no está dentro del rango 678930.0 a 1115385.0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Samsung A03 core</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>Motorola Moto G05 256Gb Verde</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>662100</v>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0936</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Samsung A03s 64GB</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>Oppo A5M 256Gb 4G Blanco</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1002100</v>
+      </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0915</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SAMSUNG A04 128GB 4RAM</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>Xiaomi Redmi 15C 128Gb Azul</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>652100</v>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0924</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SAMSUNG A04E 64GB 3GB RAM</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>Xiaomi Redmi 15C 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>722100</v>
+      </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0925</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SAMSUNG A04S 64GB 4 RAM</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>Xiaomi Redmi 15C 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>722100</v>
+      </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0934</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>722100.0 no está dentro del rango 821940.0 a 1500000.0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SAMSUNG A05S 128GB 6RAM</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>Samsung Galaxy A36 256Gb 5G Negro</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1722150</v>
+      </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0171</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Samsung A12 128GB</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
+          <t>Samsung Galaxy A17 256Gb Azul</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1122100</v>
+      </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0951</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Samsung A12 64GB</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>Samsung Galaxy A26 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1122100</v>
+      </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0822</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Samsung A13 128gb</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>Honor X7D 256Gb Negro</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>972100</v>
+      </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0969</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SAMSUNG A13 128GB + POSTPAGO 60 GB +ACCESORIO</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>Oppo A5 256Gb 4G Blanco</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>812100</v>
+      </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0914</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>812100.0 no está dentro del rango 880000.0 a 1094900.0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SAMSUNG A13 128GB 6 RAM</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+          <t>Honor 400 Lite 256Gb Gris</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1215100</v>
+      </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0846</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Samsung A13 64gb</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>Honor X5C 128Gb Plata</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>622100</v>
+      </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0939</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SAMSUNG A13 64GB + POSTPAGO 60 GB +ACCESORIO</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
+          <t>Tecno Mobile Sprk Go 2 256Gb4G Blanco</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>652100</v>
+      </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0930</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SAMSUNG A14 5G 128GB 4 RAM</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
+          <t>Samsung Galaxy A07 128Gb Negro</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>622100</v>
+      </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0955</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SAMSUNG A15 256GB 8RAM</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
+          <t>Motorola Moto G06 128Gb Azul</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>572100</v>
+      </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0975</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Samsung A21 128gb</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
+          <t>Tecno Mobile Camon 40 Pro256Gb Negr</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1722150</v>
+      </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0132</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>exitosa</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Samsung A21 64gb</t>
+          <t xml:space="preserve"> LAPTOP ACER 15,6" RYZEN 75700U SSD 1TB DDR4 16RAM   </t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>LP0095</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Samsung A22 128gb</t>
+          <t>098122843657 LAPTOP HP 15"INTEL CORE I3 N305 SSD512 8RAM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>LP0090</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SAMSUNG A22 5G 128GB</t>
+          <t>3669526-LAPTOP LENOVO 15,3" INTEL CORE I5-1340H SSD 512GB 8 RAM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>LP0075</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Samsung A22 64gb</t>
+          <t>HONOR 200 5G 256GB 12RAM TVPG</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0112</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SAMSUNG A23 128GB</t>
+          <t>HONOR 200 5G 512GB 12RAM TVPG</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0117</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SAMSUNG A23 64GB</t>
+          <t>HONOR 400 LITE 5G 256GB 12RAM TVPG</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0128</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SAMSUNG A25 128GB 6RAM</t>
+          <t>HONOR 400 SMART 5G 5G 256GB 12 RAM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0957</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Samsung A32 128gb</t>
+          <t>HONOR MAGIC 7 LITE 5G 512GB 8RAM TVPG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0063</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SAMSUNG A33 128 GB 6GB RAM</t>
+          <t>HONOR PLAY 9A 128GB 4 RAM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0689</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SAMSUNG A33 128GB 6GB RAM</t>
+          <t>HONOR PLAY 9A 256GB 4 RAM</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0688</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SAMSUNG GALAXY M13 128GB</t>
+          <t>HONOR PLAY 9A 64GB 4RAM</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0868</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SAMSUNG GALAXY M23 128GB</t>
+          <t>HONOR PLAY 9C 256GB 6RAM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0872</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Samsung Galaxy TAB A7 LITE</t>
+          <t>HONOR PLAY 9T 256GB 8RAM</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0862</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Samsung M12 128gb</t>
+          <t>HONOR X5B 64GB 4RAM</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0865</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TECNO CAMON 20 PRO 256GB 8RAM</t>
+          <t>HONOR X5B PLUS 256GB 4RAM</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0676</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TECNO POVA 3 128GB 6RAM</t>
+          <t>HONOR X5C 64GB 4RAM</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0938</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TECNO POVA 5 5G 256GB 8RAM</t>
+          <t>HONOR X6B 128GB 4 RAM</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0242</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TECNO SPARK 10 128GB 8RAM</t>
+          <t>HONOR X6B PLUS 256GB 8RAM</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0694</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TECNO SPARK 10C 128GB 8GB RAM</t>
+          <t>HONOR X6C 128GB 6RAM</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0949</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TECNO SPARK 20C 128GB 4RAM</t>
+          <t>HONOR X7 128GB 4RAM</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0881</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TECNO SPARK 20C 256GB 8RAM</t>
+          <t>HONOR X8C 256GB 8 RAM</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0738</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>VIVO Y20 64GB 4 RAM</t>
+          <t>HONOR X9C 256 GB 8 RAM</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0784</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>VIVO Y36 128GB 8RAM</t>
+          <t>HONOR X9C SMART 256GB 8RAM</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0844</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>VIVO Y53S 128GB 8 RAM</t>
+          <t>INFINIX GT 30 256GB 8+8 RAM</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0950</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>XIAOMI NOTE 10 64GB 4GB RAM</t>
+          <t>INFINIX GT 30 PRO 256GB 12RAM TVPG</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0133</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>XIAOMI NOTE 12 PRO 256GB 8RAM</t>
+          <t>INFINIX GT 30 PRO 512GB 12RAM TVPG</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>TVP0161</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>XIAOMI NOTE 8 128GB 4GB RAM</t>
+          <t>INFINIX HOT 40 PRO 8RAM 256GB</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0185</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>XIAOMI NOTE 8 64GB 4GB RAM</t>
+          <t>INFINIX HOT 40I 256 GB 8RAM</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0164</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>XIAOMI POCO M4/PRO-5G 128GB 6RAM</t>
+          <t>INFINIX HOT 50 256GB 8RAM</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0632</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>XIAOMI REDMI 10 2022 128GB 4RAM</t>
+          <t>INFINIX HOT 50 5G 256GB 8RAM</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0636</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 10 2022 64GB</t>
+          <t>INFINIX HOT 50 PRO 256GB 16 RAM</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0690</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 10 64GB</t>
+          <t>INFINIX HOT 50 PRO+ 256GB 16 RAM</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0664</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>XIAOMI REDMI 10C 128GB 4GB RAM</t>
+          <t>INFINIX HOT 50I 256GB 8 RAM</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0618</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>XIAOMI REDMI 10C 64GB 3RAM</t>
+          <t>INFINIX HOT 50I 256GB 8+8 RAM</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0740</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi 9A 32GB</t>
+          <t>INFINIX HOT 60 PRO 256GB 8+8RAM</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0948</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>XIAOMI REDMI 9C 128GB 4RAM</t>
+          <t>INFINIX HOT 60 PRO+ 256GB 8+8RAM</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0918</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>XIAOMI REDMI 9C 64GB 3RAM</t>
+          <t xml:space="preserve">INFINIX HOT 60I 256GB 4+4RAM </t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0919</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>XIAOMI REDMI A2 32GB 2GB RAM</t>
+          <t>INFINIX HOT 60i 256GB 8+8RAM</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0945</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>XIAOMI REDMI A2 64GB 2RAM</t>
+          <t>INFINIX HOT 60I 5G 256GB 8RAM</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0960</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi Note 10S 64GB</t>
+          <t>INFINIX NOTE 40 256GB 8RAM</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0200</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi Note 11 64GB</t>
+          <t>INFINIX NOTE 40 PRO 256GB 8RAM</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0211</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>XIAOMI REDMI NOTE 12S 256 GB 8 RAM</t>
+          <t>INFINIX NOTE 40 PROPLUS 5G 256GB 24RAM</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0219</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Y15S 64GB 4GB RAM</t>
+          <t>INFINIX NOTE 50 PRO 256GB 12+12RAM</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0840</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Y20S 128GB 4GB RAM</t>
+          <t>INFINIX NOTE 50 PRO 256GB 8+8RAM</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0878</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Y21S 128GB 4GB RAM</t>
+          <t>INFINIX NOTE 50S 5G 256GB 8+8RAM</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0841</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Y33S 128GB 8GB RAM</t>
+          <t>INFINIX SMART 10 128GB 4+4RAM</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
-          <t>producto sin traduccion</t>
+          <t>T0888</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>INFINIX SMART 10 256GB 4+4RAM</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>T0889</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>INFINIX SMART 10 64GB 3+3 RAM</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>T0887</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>INFINIX SMART 8 128GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>T0183</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>INFINIX SMART 8 64GB 3RAM</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>T0165</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>INFINIX SMART 8 PRO 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>T0218</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>INFINIX SMART 9HD 64GB 6 RAM</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>T0684</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>LAPTOP ACER 15 6 INTEL CORE I5 SSD 512GB DDR4 16RAM</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>LP0065</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>LAPTOP ACER 15,6  INTEL CI3 1215U 15,6" FHD 512GB SSD  8RAM</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>LP0105</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>LAPTOP ACER 15,6 INTEL CORE I5 1235U ASPIRE 3 512GB DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>LP0074</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>LAPTOP ACER 15,6" RYZEN 7 5700U ASPIRE LITE 512GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>LP0119</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>LAPTOP ACER 15,6" RYZEN 7 5700U SSD 1TB DDR4 16RAM</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>LP0092</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>LAPTOP ACER 15,7 RYZEN R5 7520U 15,6" FHD TOUCH 512SSD 16RAM</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>LP0106</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>LAPTOP ASUS 15" INTEL I7 CORE 13620H SSD 1 TB DDR4 16GB</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>LP0126</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>LAPTOP ASUS 15,6" vivobook RYZEN 5 7520U SSD 512GB 16RAM</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>LP0063</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>LAPTOP ASUS 15.6 INTEL CORE I3 N305 SSD 512GB DDR4 8GB</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>LP0084</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>LAPTOP ASUS 15.6" INTELI CORE 12VA GENERACION ASUS VIVOBOOK SSD 512GB DDR4 4GB + 8RAM</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>LP0102</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>LAPTOP DELL 15 6" INTEL CORE I31215U SSD 512GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>LP0066</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>LAPTOP DELL INTEL CORE 7-1235U DELL INSPIRON15 SSD 512GB DDR5 8RAM</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>LP0059</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14 INTEL CELERON N4500 SSD 512GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>LP0121</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14 INTEL CORE I5-1235U 14-dq5016la SSD 512 8RAM</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>LP0071</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14 INTEL CORE I5-1235U 14-DQ5039IA 512GB 4 8RAM</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>LP0073</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14 RYZEN 3 7320U em0005la SSD 512GB DRR5 8GB</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>LP0128</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14 RYZEN 3 7330U HP 245 G10 7330U SSD 512GB DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>LP0067</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14 RYZEN 5 5625U HP 245 G9 SSD 256GB DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>LP0068</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14 RYZEN 5 7520U SSD 512GB DDR5 16GB</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>LP0083</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14" INTEL CELERON N4120 SSD2 56GB DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>LP0058</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14" INTEL CELERON N4500 LED 14" SSD 512GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>LP0107</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14" INTEL CELERON N4500 SSD 256GB DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>LP0088</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14" RYZEN 5 7520U SSD 512GB DDR 8RAM</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>LP0086</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 14" RYZEN 5 SSD 256GB DDR5 8RAM</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>LP0056</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAPTOP HP 14" RYZEN R3 7320U 14" FHD SSD 512GB 8RAM </t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>LP0108</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAPTOP HP 14" RYZEN R5 7520U 14" FHD SSD 512GB 16RAM </t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>LP0109</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAPTOP HP 15" RYZEN 5 7520U 512GB 8RAM </t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>LP0118</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAPTOP HP 15,6" RIZEN R7 7730U 15,6 FHD 512GB SSD 16RAM </t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>LP0110</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 15,6" RYZEN 5 7520U SSD 1TB DDR5 16RAM</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>LP0094</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 15.6" INTEL CORE I5 120U SSD 512GB DDR4 16GB</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>LP0111</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 15.6" INTEL CORE I5 120U SSD 512GB DDR4 16RAM</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>LP0112</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 15.6" INTEL i3 1215U 15-fd0023dx touchscreen SSD 256GB DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>LP0101</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 15.6" RYZEN 3 7320U 255G-10 SSD 512GB 16RAM</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>LP0091</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>LAPTOP HP 15.6” HP RYZEN 7 5700U SSD 512GB 16RAM</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>LP0057</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 14" INTEL i5-13420H 2.1GHz V14 G4 SSD 512 GB DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>LP0089</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 14" RYZEN 3 732U 256GB SSD 16RAM</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>LP0125</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 14" RYZEN 7 7730U LENOVO V14 512 GB 8 GB</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>LP0123</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 14" RYZEN RYZEN 5 7520U SSD 256GB DDR5 16RAM NOTEBOOK</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>LP0122</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 14" RYZEN RYZEN 5 7520U SSD 512GB DDR5 16RAM NOTEBOOK</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>LP0116</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15" AMD Athlon Silver 7120U 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>LP0127</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15" INTEL CELERON N4020 IDEA PAD1 SSD 256GB DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>LP0060</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15" RYZEN 7 5825U Lenovo IdeaPad Slim 3 15ABR8 SSD 512GB DDR4 16 RAM</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>LP0087</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15,6" INTEL   CI5 15IRH1 SSDD 512GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>LP0114</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15,6" INTEL  CI3 1315U SSDD 512GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>LP0113</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15,6" INTEL CORE I3 N305 512GB SSD 8GB DDR4</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>LP0124</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15,6" INTEL CORE I5 1235U IDEAPAD 1 SSD512GB DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>LP0064</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15,6" INTEL I3-1315U SSD 512GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>LP0096</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15.6 INTEL I3-N305 IDEAPAD SLIM 3 15IAN8 512GB 4 8RAM</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>LP0072</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15.6" INTEL INTEL i5 -13420H SSD 512GB DDR4 16RAM NOTE BOOK</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>LP0115</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15.6" INTELi3-1215U ideapad 3 ssd 512GB DDR5 8RAM</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>LP0098</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15.6" RYZEN 5 7520U ideapad 1 touchscreen ssd 256GB DDR5 8RAM</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>LP0097</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>LAPTOP LENOVO 15.6" RYZEN RYZEN 5 7520U SSD 512GB DDR5 16RAM</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>LP0117</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>LAPTOP SAMSUNG 1,5" INTEL i5-1335U galaxy book 4 np750xgj SSD 512GB 16RAM</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>LP0099</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>LAPTOP SAMSUNG 15 6 INTEL CORE I7 1355U Vivabook4 SSD 512GB DDR 4 16GB</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>LP0080</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>LAPTOP SAMSUNG 15"6 INTEL ICORE 5 120U galaxy book4 np750xgk-ka1cl SSD 512GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>LP0100</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>LAPTOS HP RYZEN 37330U SSD512 DDR4 8RAM</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>LP0061</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>MONTO MAXIMO DEL CREDITO LB 2.5M</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>LB0002</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>MONTO MAXIMO DEL CREDITO LB 2M</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>LB0003</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>MONTO MAXIMO DEL CREDITO LB 3M</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>LB0001</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>MONTO MÁXIMO DEL CREDITO TV 1.4M</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>TV0003</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>MONTO MAXIMO DEL CREDITO TV 2.5M</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>TV0001</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>MONTO MAXIMO DEL CREDITO TV 2M</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>TV0002</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>MOTO G52 128GB 6 RAM</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>T0091</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>MOTOROLA E14 64GB 2 RAM</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>T0245</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>MOTOROLA E15 64GB 2GB RAM</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>T0805</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>MOTOROLA EDGE 40 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>TVP0118</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>MOTOROLA EDGE 50 FUSION 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>T0611</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>MOTOROLA EDGE 50 FUSION 512GB 12RAM</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>T0869</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>MOTOROLA EDGE 60 512GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>TVP0122</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>MOTOROLA G05 128GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>T0713</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>MOTOROLA G06 256GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>T0974</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>MOTOROLA G15 128GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>T0736</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>MOTOROLA G15 256GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>T0714</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>MOTOROLA G24 256GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>T0227</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>MOTOROLA G35 5G 256 8RAM</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>T0884</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>MOTOROLA G55 5G 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>T0699</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>MOTOROLA G56 5G 256GB 8 RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>TVP0139</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>MOTOROLA G75 5G 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>T0706</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>MOTOROLA G85 5G 512GB 12RAM</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>T0922</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>MOTOROLA G86 5G 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>T0962</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>OPPO A20 128GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>T0602</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>OPPO A5 PRO 5G 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>TVP0126</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPPO A5X 128GB 4+4RAM </t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>T0933</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>OPPO RENO 10 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>T0885</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>OPPO RENO 11 5G 256GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>TVP0104</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>OPPO RENO 12 512GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>TVP0059</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>OPPO RENO 12F 5G 256GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>TVP0130</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>OPPO RENO 13F 5G 256GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>TVP0169</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>OPPO RENO 13F 5G 512GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>TVP0110</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>OPPO RENO 14F 5G 256GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>TVP0165</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>POCO F7 512GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>TVP0121</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>POCO F7 PRO 512GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>TVP0120</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>POCO M7 PRO 5G 512GB 12RAM</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>T0966</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>POCO X7 PRO 256GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>TVP0131</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>POCO X7 PRO 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>TVP0138</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>POCO X7 PRO 5G 512GB 12 RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>TVP0127</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>PORTATIL ACER A315 59 37Q9 FHD CI3 1215U 15,6" 8GB 512SSD</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>LP0041</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>PORTATIL ACER A315-510P 34LK FHD CI3 N305 15,6" 8GB DDR5 4GBX2 512GB SSD</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>LP0040</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>PORTATIL ACER AG14 31P 35FJ CI3 N305 14" IPS , WUXGA 1920 X1200 COMFYVIEW LCD 8GB DDR4 512SSD</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>LP0042</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>PORTATIL ACER ASPIRE 54M4 CI5 15.6" 8GB 512GB</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>LP0043</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Portatil ACER Aspire Lite Intel Core i3 N300 RAM 8 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>LP0034</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Portatil ACER Corporativa Intel Core i3 1315U RAM 16 GB 1 TB</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>LP0033</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Portatil ACER Corporativa Intel Core i3 1315U RAM 16 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>LP0032</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>PORTATIL ASUS E1504GANJ330W CORE I3N305 8GB 512GB W11H</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>LP0044</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>PORTATIL ASUS EXPERTBOOK 14" B1402CVA CORE I5 DISCO SSD 512SSD 8RAM</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>LP0037</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Portatil ASUS Vivobook 15 Intel Core i5 1235U RAM 8 GB 1 TB</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>LP0031</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Portatil ASUS Vivobook 15 Intel Core i5 1235U RAM 8 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>LP0030</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Portatil ASUS Vivobook 15 Intel Core i5 12500H RAM 8 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>LP0029</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>PORTATIL ASUS VIVOBOOK 15.6" X1504ZA-NJ1200 CORE I3 1215U DISCO SSD 512 12RAM</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>LP0038</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Portatil ASUS Vivobook Go 15 Intel Core i3 N305 RAM 8 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr"/>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>LP0028</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>PORTATIL DELL 3520 CORE I5 1235U 8+512SSD 15.6"</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>LP0039</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>PORTATIL DELL INSPIRON CORE I7 1255U 4.7GHZ 10C RAM 8GB SSD 512GB PANT 15,6"</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>LP0045</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>PORTATIL DELL PORTATIL 5480 I5 6TA 8GB 128SSD</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr"/>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>LP0046</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>PORTATIL HP 14" DQ5011LA CORE i3 1215U DISCO SSD 512 8RAM</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr"/>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>LP0036</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Portatil HP Intel Core i3 1215U RAM 8 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr"/>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>LP0027</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Portatil HP Intel Core i5 1334U RAM 8 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr"/>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>LP0026</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Portatil HP Intel Core Ultra 5 Ultra125H RAM 8 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr"/>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>LP0035</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>PORTATIL LENOVO IDEAPAD 15.6" FHD TOUCHSCREEN IC I3-1215U 8GB RAM 256GB</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>LP0051</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORTATIL LENOVO IDEAPAD SLIM 3 15IRH8 INTEL CORE I7 13620H 15,6" FHD 16GB 512GB WINDOWS 11 </t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr"/>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>LP0053</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Portatil LENOVO IdeaPad Slim 3 Intel Core i3 N305 RAM 8 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>LP0025</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Portatil LENOVO Intel Core i5 12450H RAM 8 GB 512 GB IdeaPad Slim 3</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>LP0024</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Portatil LENOVO Intel Core i5 1245H RAM 16 GB 512 GB IdeaPad Slim 5</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>LP0023</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>PORTATIL LENOVOI DEAPAD SLIM 3 15IAH8 INTEL CORE I5-12450H 15,6 FHD MEMORIA 16GB SSD 512GB</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>LP0052</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>PORTATIL SAMSUNG GALAXY BOOK4 NP750XGK KA1CL WIN11 HOME INTEL CORE 5 ULTRA 120U 8GB SSD 512GB</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>LP0054</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Portatil Tactil ACER Spin Intel Core i3 100U RAM 8 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>LP0022</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Portatil Tactil LENOVO IdeaPad Slim 3 Intel Core i5 12450H RAM 16 GB 512 GB</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>LP0021</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Portatil Tactil LENOVO Intel Core i5 12450H RAM 8 GB 512 GB IdeaPad Slim 3</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>LP0020</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>REALME 14 5G 256GB 8+8RAM</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>T0848</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>REALME 14 PRO 5G 256GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>TVP0143</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>REALME 15T 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>T0968</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>REALME C51 128GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>T0192</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>REALME C51 256GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>T0605</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>REALME C53 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>T0101</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>REALME C53 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>T0178</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>REALME C55 256GB 8 RAM</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>T0099</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>REALME C61 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>T0635</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>REALME C67 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>T0179</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>REALME C71 128GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>T0907</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>REALME C71 256GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>T0908</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>REALME C75 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>T0909</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>REALME C75 5G 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>T0910</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REALME C75 5G 256GB 8RAM </t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>T0928</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>REALME NOTE 50 128GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>T0205</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>REALME NOTE 50 256GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>T0711</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>REALME NOTE 50 64GB 3RAM</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>T0232</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>REALME NOTE 60X 128GB 4+8RAM</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>T0843</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>REALME NOTE 60X 64GB 3RAM</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>T0852</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>REALME NOTE 70 256GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>T0946</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>REALME NOTE 70 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>T0947</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>REALME 15 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>TVP0172</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>REDMI 13X 256GB 8 RAM</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>T0859</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>REDMI 15 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>T0926</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>REDMI 15 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>T0927</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>REDMI A5 64GB 3 RAM</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>T0220</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 13 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>T0176</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 13 128GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>T0837</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 13 PRO+ 5G 512GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>TVP0134</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 14 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>T0709</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 14 PRO 5G 256GB 8 RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>TVP0142</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 14 PRO+ 5G 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>TVP0065</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 14 PRO+ 5G 512GB 12RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>TVP0170</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Samsug Galaxy S24 FE 5G 128GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>TVP0113</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>SAMSUNG A05S 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>T0163</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>SAMSUNG A06 64GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>T0601</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>SAMSUNG A16 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>T0779</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>SAMSUNG A25 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>T0160</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>SAMSUNG A35 5G 256GB 8 RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>TVP0125</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>SAMSUNG A55 256GB 8 RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>TVP0062</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>SAMSUNG GALAXY A07 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>T0959</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>SAMSUNG GALAXY A07 64GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>T0956</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>SAMSUNG GALAXY A16 128GB 4 RAM</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>T0851</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>SAMSUNG GALAXY A16 5G 128GB 6 RAM</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>T0820</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>SAMSUNG GALAXY A17 128GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>T0954</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>SAMSUNG GALAXY A17 128GB 6RAM</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr"/>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>T0953</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>SAMSUNG GALAXY A17 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>T0952</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>SAMSUNG GALAXY S21 FE 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>TVP0061</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>SAMSUNG GALAXY S22 FE 128GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>TVP0060</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>SAMSUNG M55 5G 256GB 8 RAM</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>T0812</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>SPARK 40 PRO 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>T0912</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>SPARK 40 PRO+ 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>T0911</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>SPARK 40 PRO+ 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>TVP0129</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>TECNO CAMON 30 5G 256GB 8 GB RAM</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>T0814</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>TECNO CAMON 30 5G 512GB 8+8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>TVP0140</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>TECNO CAMON 30S 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>T0658</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>TECNO CAMON 30S PRO 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>T0598</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>TECNO CAMON 40 256GB 8+8 RAM</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>T0765</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>TECNO POVA 5 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>T0813</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>TECNO POVA 5 5G 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>T0143</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>TECNO POVA 5 PRO 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>T0634</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>TECNO POVA 6 5G 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>T0839</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>TECNO POVA 7 256GB 8 RAM</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>T0893</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Tecno Pova 7 5G 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>T0941</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>TECNO SPARK 20C 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>T0175</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>TECNO SPARK 30 256GB 8 RAM</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>T0619</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>TECNO SPARK 30 PRO 256GB 8 RAM</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>T0617</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>TECNO SPARK 30C 128GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>T0603</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>TECNO SPARK 40 256GB 4RAM</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>T0906</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>TECNO SPARK GO 1 64GB 3RAM</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>T0614</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>TECNO SPARK GO 1S 64GB 3RAM</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>T0691</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>TECNO SPARK GO 2 128GB 4 RAM</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>T0894</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>TECNO SPARK GO 2 64GB 3 RAM</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>T0895</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>VIVO V30 512GB 12 RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>TVP0064</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>VIVO V40 LITE 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>T0913</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>VIVO V50 LITE 256GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>T0920</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>VIVO V50 LITE 5G 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>TVP0135</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>VIVO V60 LITE 5G 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>TVP0173</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>VIVO Y04 128GB 4 RAM</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>T0809</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>VIVO Y19 S PRO 256GB 8RAM TVPG</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>TVP0141</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>XIAOMI 12 PRO 5G 256GB 12RAM</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>T0832</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>XIAOMI POCO X7 256GB 8 RAM</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>T0879</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>XIAOMI REDMI 13C 8GB RAM 256GB</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>T0247</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>XIAOMI REDMI NOTE 12S 256 GB 8 RAM</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>T0112</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>XIAOMI REDMI NOTE 13 512GB 8RAM</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>T0659</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>XIAOMI REDMI NOTE 14S 256GB 8 RAM</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>T0811</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>producto en pagina pero no en excel</t>
         </is>
       </c>
     </row>
